--- a/hardware_teams.xlsx
+++ b/hardware_teams.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="671">
   <si>
     <t>SIH 2026 — Final Teams (Hardware)</t>
   </si>
@@ -977,6 +977,71 @@
     <t>7358832267</t>
   </si>
   <si>
+    <t xml:space="preserve">it006
+[Ministry: Ministry of Coal (MoC)]
+[PS: SIH26025 (Hardware)]</t>
+  </si>
+  <si>
+    <t>SANKARI K</t>
+  </si>
+  <si>
+    <t>25UIT188</t>
+  </si>
+  <si>
+    <t>8531081731</t>
+  </si>
+  <si>
+    <t>Information Technology · Year II · Sec A</t>
+  </si>
+  <si>
+    <t>JAGATHISH P</t>
+  </si>
+  <si>
+    <t>25UIT066</t>
+  </si>
+  <si>
+    <t>9442029084</t>
+  </si>
+  <si>
+    <t>KIRTHAAN</t>
+  </si>
+  <si>
+    <t>25UIT096</t>
+  </si>
+  <si>
+    <t>8072220967</t>
+  </si>
+  <si>
+    <t>RUPASHREE GOWRISHANKAR</t>
+  </si>
+  <si>
+    <t>25UIT178</t>
+  </si>
+  <si>
+    <t>9092056465</t>
+  </si>
+  <si>
+    <t>HARISH SKANDAN S</t>
+  </si>
+  <si>
+    <t>25UEC056</t>
+  </si>
+  <si>
+    <t>8148373977</t>
+  </si>
+  <si>
+    <t>Electronics and Communication Engineering · Year II · Sec A</t>
+  </si>
+  <si>
+    <t>JAGANNATH S</t>
+  </si>
+  <si>
+    <t>25UME034</t>
+  </si>
+  <si>
+    <t>9345404761</t>
+  </si>
+  <si>
     <t xml:space="preserve">KYNORA
 [Ministry: Ministry of Development of North Eastern Region (MoDoNER)]
 [PS: SIH26004 (Hardware)]</t>
@@ -1104,6 +1169,65 @@
     <t>7825049956</t>
   </si>
   <si>
+    <t xml:space="preserve">MCTRFINAL#01
+[Ministry: Ministry of Defence (MoD)]
+[PS: SIH26098 (Hardware)]</t>
+  </si>
+  <si>
+    <t>YOVEL V</t>
+  </si>
+  <si>
+    <t>25UMT059</t>
+  </si>
+  <si>
+    <t>9003423721</t>
+  </si>
+  <si>
+    <t>SAM YANNICK E</t>
+  </si>
+  <si>
+    <t>25UMT043</t>
+  </si>
+  <si>
+    <t>8056462179</t>
+  </si>
+  <si>
+    <t>VIGNESH YADAV K</t>
+  </si>
+  <si>
+    <t>25UMT058</t>
+  </si>
+  <si>
+    <t>7092202849</t>
+  </si>
+  <si>
+    <t>AMERDA KEISHORRIEE SUNDARAM ROSE</t>
+  </si>
+  <si>
+    <t>25UMT004</t>
+  </si>
+  <si>
+    <t>9629358548</t>
+  </si>
+  <si>
+    <t>RANJANIPRIYA S</t>
+  </si>
+  <si>
+    <t>25UCS202</t>
+  </si>
+  <si>
+    <t>8428188456</t>
+  </si>
+  <si>
+    <t>NETHRA R</t>
+  </si>
+  <si>
+    <t>25UCS163</t>
+  </si>
+  <si>
+    <t>9363079356</t>
+  </si>
+  <si>
     <t xml:space="preserve">phoenix coders
 [Ministry: Ministry of Home Affairs (MHA)]
 [PS: SIH26189 (Hardware)]</t>
@@ -1183,9 +1307,6 @@
     <t>9092365426</t>
   </si>
   <si>
-    <t>Information Technology · Year II · Sec A</t>
-  </si>
-  <si>
     <t>HARIHARAN D</t>
   </si>
   <si>
@@ -1220,9 +1341,6 @@
   </si>
   <si>
     <t>9042219858</t>
-  </si>
-  <si>
-    <t>Electronics and Communication Engineering · Year II · Sec A</t>
   </si>
   <si>
     <t>KRISHNARAJ.K</t>
@@ -2427,7 +2545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I182"/>
+  <dimension ref="A1:I194"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4375,7 +4493,7 @@
         <v>315</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>23</v>
+        <v>316</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>24</v>
@@ -4391,19 +4509,19 @@
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="D88" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="G88" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
@@ -4412,16 +4530,16 @@
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>15</v>
@@ -4442,10 +4560,10 @@
         <v>325</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
@@ -4463,10 +4581,10 @@
         <v>328</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>23</v>
+        <v>329</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
@@ -4475,19 +4593,19 @@
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
@@ -4497,19 +4615,19 @@
         <v>16</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>336</v>
+        <v>23</v>
       </c>
       <c r="G93" s="6" t="s">
         <v>24</v>
@@ -4534,7 +4652,7 @@
         <v>339</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>336</v>
+        <v>23</v>
       </c>
       <c r="G94" s="6" t="s">
         <v>24</v>
@@ -4555,10 +4673,10 @@
         <v>342</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H95" s="6"/>
       <c r="I95" s="6"/>
@@ -4567,19 +4685,19 @@
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F96" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="D96" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>336</v>
-      </c>
       <c r="G96" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H96" s="6"/>
       <c r="I96" s="6"/>
@@ -4588,16 +4706,16 @@
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>349</v>
+        <v>23</v>
       </c>
       <c r="G97" s="6" t="s">
         <v>24</v>
@@ -4618,10 +4736,10 @@
         <v>352</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>349</v>
+        <v>23</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H98" s="6"/>
       <c r="I98" s="6"/>
@@ -4643,10 +4761,10 @@
         <v>356</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>138</v>
+        <v>357</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>16</v>
@@ -4659,19 +4777,19 @@
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="F100" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="D100" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="G100" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
@@ -4680,19 +4798,19 @@
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
@@ -4710,7 +4828,7 @@
         <v>366</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>24</v>
@@ -4722,16 +4840,16 @@
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="E103" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="E103" s="4" t="s">
+      <c r="F103" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>24</v>
@@ -4752,10 +4870,10 @@
         <v>373</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
@@ -4777,7 +4895,7 @@
         <v>377</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="G105" s="6" t="s">
         <v>15</v>
@@ -4793,16 +4911,16 @@
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="D106" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="E106" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="E106" s="6" t="s">
-        <v>381</v>
-      </c>
       <c r="F106" s="6" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="G106" s="6" t="s">
         <v>15</v>
@@ -4814,19 +4932,19 @@
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="D107" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="E107" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="E107" s="6" t="s">
-        <v>384</v>
-      </c>
       <c r="F107" s="6" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H107" s="6"/>
       <c r="I107" s="6"/>
@@ -4835,16 +4953,16 @@
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="D108" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="D108" s="6" t="s">
+      <c r="E108" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="E108" s="6" t="s">
-        <v>387</v>
-      </c>
       <c r="F108" s="6" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="G108" s="6" t="s">
         <v>24</v>
@@ -4856,19 +4974,19 @@
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D109" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="D109" s="6" t="s">
+      <c r="E109" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="E109" s="6" t="s">
-        <v>390</v>
-      </c>
       <c r="F109" s="6" t="s">
-        <v>391</v>
+        <v>209</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
@@ -4877,19 +4995,19 @@
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="E110" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="D110" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="E110" s="6" t="s">
-        <v>394</v>
-      </c>
       <c r="F110" s="6" t="s">
-        <v>391</v>
+        <v>209</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
@@ -4899,19 +5017,19 @@
         <v>19</v>
       </c>
       <c r="B111" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="E111" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D111" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="E111" s="4" t="s">
-        <v>398</v>
-      </c>
       <c r="F111" s="4" t="s">
-        <v>363</v>
+        <v>138</v>
       </c>
       <c r="G111" s="4" t="s">
         <v>15</v>
@@ -4927,16 +5045,16 @@
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E112" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="D112" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>401</v>
-      </c>
       <c r="F112" s="4" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>15</v>
@@ -4948,16 +5066,16 @@
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E113" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="D113" s="4" t="s">
+      <c r="F113" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="E113" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="F113" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="G113" s="4" t="s">
         <v>15</v>
@@ -4969,19 +5087,19 @@
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="E114" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="E114" s="4" t="s">
+      <c r="F114" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="F114" s="4" t="s">
-        <v>363</v>
-      </c>
       <c r="G114" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
@@ -4999,7 +5117,7 @@
         <v>410</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>411</v>
+        <v>130</v>
       </c>
       <c r="G115" s="4" t="s">
         <v>24</v>
@@ -5011,16 +5129,16 @@
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="D116" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="E116" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="E116" s="4" t="s">
-        <v>414</v>
-      </c>
       <c r="F116" s="4" t="s">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="G116" s="4" t="s">
         <v>24</v>
@@ -5033,19 +5151,19 @@
         <v>20</v>
       </c>
       <c r="B117" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="C117" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="C117" s="6" t="s">
+      <c r="D117" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="D117" s="6" t="s">
+      <c r="E117" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="E117" s="6" t="s">
-        <v>418</v>
-      </c>
       <c r="F117" s="6" t="s">
-        <v>228</v>
+        <v>316</v>
       </c>
       <c r="G117" s="6" t="s">
         <v>15</v>
@@ -5061,16 +5179,16 @@
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D118" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="D118" s="6" t="s">
+      <c r="E118" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="E118" s="6" t="s">
-        <v>421</v>
-      </c>
       <c r="F118" s="6" t="s">
-        <v>228</v>
+        <v>316</v>
       </c>
       <c r="G118" s="6" t="s">
         <v>15</v>
@@ -5082,19 +5200,19 @@
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="D119" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="D119" s="6" t="s">
+      <c r="E119" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="E119" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="F119" s="6" t="s">
-        <v>228</v>
+        <v>316</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H119" s="6"/>
       <c r="I119" s="6"/>
@@ -5103,19 +5221,19 @@
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="D120" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="D120" s="6" t="s">
+      <c r="E120" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="E120" s="6" t="s">
-        <v>427</v>
-      </c>
       <c r="F120" s="6" t="s">
-        <v>228</v>
+        <v>316</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H120" s="6"/>
       <c r="I120" s="6"/>
@@ -5124,19 +5242,19 @@
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D121" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="D121" s="6" t="s">
+      <c r="E121" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="E121" s="6" t="s">
-        <v>430</v>
-      </c>
       <c r="F121" s="6" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
@@ -5145,19 +5263,19 @@
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="D122" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="D122" s="6" t="s">
+      <c r="E122" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="E122" s="6" t="s">
-        <v>433</v>
-      </c>
       <c r="F122" s="6" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H122" s="6"/>
       <c r="I122" s="6"/>
@@ -5167,19 +5285,19 @@
         <v>21</v>
       </c>
       <c r="B123" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C123" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="D123" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="E123" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="E123" s="4" t="s">
-        <v>437</v>
-      </c>
       <c r="F123" s="4" t="s">
-        <v>438</v>
+        <v>403</v>
       </c>
       <c r="G123" s="4" t="s">
         <v>15</v>
@@ -5195,16 +5313,16 @@
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="E124" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="D124" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>441</v>
-      </c>
       <c r="F124" s="4" t="s">
-        <v>438</v>
+        <v>14</v>
       </c>
       <c r="G124" s="4" t="s">
         <v>15</v>
@@ -5216,16 +5334,16 @@
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="E125" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="D125" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="E125" s="4" t="s">
-        <v>444</v>
-      </c>
       <c r="F125" s="4" t="s">
-        <v>438</v>
+        <v>403</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>15</v>
@@ -5237,19 +5355,19 @@
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E126" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="D126" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="E126" s="4" t="s">
-        <v>447</v>
-      </c>
       <c r="F126" s="4" t="s">
-        <v>438</v>
+        <v>403</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H126" s="4"/>
       <c r="I126" s="4"/>
@@ -5258,16 +5376,16 @@
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="E127" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="D127" s="4" t="s">
+      <c r="F127" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="E127" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>367</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>24</v>
@@ -5279,16 +5397,16 @@
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="D128" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="E128" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="E128" s="4" t="s">
-        <v>453</v>
-      </c>
       <c r="F128" s="4" t="s">
-        <v>272</v>
+        <v>82</v>
       </c>
       <c r="G128" s="4" t="s">
         <v>24</v>
@@ -5301,19 +5419,19 @@
         <v>22</v>
       </c>
       <c r="B129" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="C129" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="C129" s="6" t="s">
+      <c r="D129" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="D129" s="6" t="s">
+      <c r="E129" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="E129" s="6" t="s">
-        <v>457</v>
-      </c>
       <c r="F129" s="6" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="G129" s="6" t="s">
         <v>15</v>
@@ -5329,16 +5447,16 @@
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="D130" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="D130" s="6" t="s">
+      <c r="E130" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="E130" s="6" t="s">
-        <v>460</v>
-      </c>
       <c r="F130" s="6" t="s">
-        <v>461</v>
+        <v>228</v>
       </c>
       <c r="G130" s="6" t="s">
         <v>15</v>
@@ -5350,19 +5468,19 @@
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="E131" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="D131" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>464</v>
-      </c>
       <c r="F131" s="6" t="s">
-        <v>303</v>
+        <v>228</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H131" s="6"/>
       <c r="I131" s="6"/>
@@ -5371,19 +5489,19 @@
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="E132" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="D132" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="E132" s="6" t="s">
-        <v>467</v>
-      </c>
       <c r="F132" s="6" t="s">
-        <v>303</v>
+        <v>228</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H132" s="6"/>
       <c r="I132" s="6"/>
@@ -5392,19 +5510,19 @@
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="E133" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="D133" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="E133" s="6" t="s">
-        <v>470</v>
-      </c>
       <c r="F133" s="6" t="s">
-        <v>99</v>
+        <v>370</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H133" s="6"/>
       <c r="I133" s="6"/>
@@ -5413,16 +5531,16 @@
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="E134" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="D134" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="E134" s="6" t="s">
-        <v>473</v>
-      </c>
       <c r="F134" s="6" t="s">
-        <v>95</v>
+        <v>370</v>
       </c>
       <c r="G134" s="6" t="s">
         <v>24</v>
@@ -5435,19 +5553,19 @@
         <v>23</v>
       </c>
       <c r="B135" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="E135" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="D135" s="4" t="s">
+      <c r="F135" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="E135" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="F135" s="4" t="s">
-        <v>138</v>
       </c>
       <c r="G135" s="4" t="s">
         <v>15</v>
@@ -5463,16 +5581,16 @@
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="D136" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="D136" s="4" t="s">
+      <c r="E136" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="E136" s="4" t="s">
-        <v>480</v>
-      </c>
       <c r="F136" s="4" t="s">
-        <v>138</v>
+        <v>476</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>15</v>
@@ -5484,16 +5602,16 @@
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="D137" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="D137" s="4" t="s">
+      <c r="E137" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="E137" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="F137" s="4" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>15</v>
@@ -5505,19 +5623,19 @@
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="E138" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="D138" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="E138" s="4" t="s">
-        <v>487</v>
-      </c>
       <c r="F138" s="4" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H138" s="4"/>
       <c r="I138" s="4"/>
@@ -5526,16 +5644,16 @@
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="E139" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="D139" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="E139" s="4" t="s">
-        <v>490</v>
-      </c>
       <c r="F139" s="4" t="s">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="G139" s="4" t="s">
         <v>24</v>
@@ -5547,16 +5665,16 @@
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="E140" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="D140" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>493</v>
-      </c>
       <c r="F140" s="4" t="s">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="G140" s="4" t="s">
         <v>24</v>
@@ -5569,19 +5687,19 @@
         <v>24</v>
       </c>
       <c r="B141" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="D141" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="C141" s="6" t="s">
+      <c r="E141" s="6" t="s">
         <v>495</v>
       </c>
-      <c r="D141" s="6" t="s">
-        <v>496</v>
-      </c>
-      <c r="E141" s="6" t="s">
-        <v>497</v>
-      </c>
       <c r="F141" s="6" t="s">
-        <v>66</v>
+        <v>205</v>
       </c>
       <c r="G141" s="6" t="s">
         <v>15</v>
@@ -5597,16 +5715,16 @@
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="E142" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="D142" s="6" t="s">
+      <c r="F142" s="6" t="s">
         <v>499</v>
-      </c>
-      <c r="E142" s="6" t="s">
-        <v>500</v>
-      </c>
-      <c r="F142" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="G142" s="6" t="s">
         <v>15</v>
@@ -5618,16 +5736,16 @@
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="D143" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="D143" s="6" t="s">
+      <c r="E143" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="E143" s="6" t="s">
-        <v>503</v>
-      </c>
       <c r="F143" s="6" t="s">
-        <v>45</v>
+        <v>303</v>
       </c>
       <c r="G143" s="6" t="s">
         <v>24</v>
@@ -5639,16 +5757,16 @@
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="D144" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="D144" s="6" t="s">
+      <c r="E144" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="E144" s="6" t="s">
-        <v>506</v>
-      </c>
       <c r="F144" s="6" t="s">
-        <v>45</v>
+        <v>303</v>
       </c>
       <c r="G144" s="6" t="s">
         <v>24</v>
@@ -5660,16 +5778,16 @@
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="D145" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="D145" s="6" t="s">
+      <c r="E145" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="E145" s="6" t="s">
-        <v>509</v>
-      </c>
       <c r="F145" s="6" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="G145" s="6" t="s">
         <v>15</v>
@@ -5681,19 +5799,19 @@
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="D146" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="D146" s="6" t="s">
+      <c r="E146" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="E146" s="6" t="s">
-        <v>512</v>
-      </c>
       <c r="F146" s="6" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H146" s="6"/>
       <c r="I146" s="6"/>
@@ -5703,19 +5821,19 @@
         <v>25</v>
       </c>
       <c r="B147" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C147" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="D147" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="D147" s="4" t="s">
+      <c r="E147" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="E147" s="4" t="s">
-        <v>516</v>
-      </c>
       <c r="F147" s="4" t="s">
-        <v>236</v>
+        <v>138</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>15</v>
@@ -5731,16 +5849,16 @@
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="D148" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="D148" s="4" t="s">
+      <c r="E148" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="E148" s="4" t="s">
-        <v>519</v>
-      </c>
       <c r="F148" s="4" t="s">
-        <v>236</v>
+        <v>138</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>15</v>
@@ -5752,16 +5870,16 @@
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="D149" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="D149" s="4" t="s">
+      <c r="E149" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="E149" s="4" t="s">
+      <c r="F149" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="F149" s="4" t="s">
-        <v>523</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>15</v>
@@ -5773,19 +5891,19 @@
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="D150" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="D150" s="4" t="s">
+      <c r="E150" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="E150" s="4" t="s">
-        <v>526</v>
-      </c>
       <c r="F150" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H150" s="4"/>
       <c r="I150" s="4"/>
@@ -5794,16 +5912,16 @@
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="D151" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="D151" s="4" t="s">
+      <c r="E151" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="E151" s="4" t="s">
-        <v>529</v>
-      </c>
       <c r="F151" s="4" t="s">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="G151" s="4" t="s">
         <v>24</v>
@@ -5815,19 +5933,19 @@
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D152" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="D152" s="4" t="s">
+      <c r="E152" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="E152" s="4" t="s">
-        <v>532</v>
-      </c>
       <c r="F152" s="4" t="s">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
@@ -5837,19 +5955,19 @@
         <v>26</v>
       </c>
       <c r="B153" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="C153" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="C153" s="6" t="s">
+      <c r="D153" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="6" t="s">
+      <c r="E153" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="E153" s="6" t="s">
-        <v>536</v>
-      </c>
       <c r="F153" s="6" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="G153" s="6" t="s">
         <v>15</v>
@@ -5865,16 +5983,16 @@
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="D154" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="D154" s="6" t="s">
+      <c r="E154" s="6" t="s">
         <v>538</v>
       </c>
-      <c r="E154" s="6" t="s">
-        <v>539</v>
-      </c>
       <c r="F154" s="6" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="G154" s="6" t="s">
         <v>15</v>
@@ -5886,16 +6004,16 @@
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D155" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="D155" s="6" t="s">
+      <c r="E155" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="E155" s="6" t="s">
-        <v>542</v>
-      </c>
       <c r="F155" s="6" t="s">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="G155" s="6" t="s">
         <v>24</v>
@@ -5907,16 +6025,16 @@
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="D156" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="D156" s="6" t="s">
+      <c r="E156" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="E156" s="6" t="s">
-        <v>545</v>
-      </c>
       <c r="F156" s="6" t="s">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="G156" s="6" t="s">
         <v>24</v>
@@ -5928,16 +6046,16 @@
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D157" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="D157" s="6" t="s">
+      <c r="E157" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="E157" s="6" t="s">
-        <v>548</v>
-      </c>
       <c r="F157" s="6" t="s">
-        <v>549</v>
+        <v>45</v>
       </c>
       <c r="G157" s="6" t="s">
         <v>15</v>
@@ -5949,16 +6067,16 @@
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="E158" s="6" t="s">
         <v>550</v>
       </c>
-      <c r="D158" s="6" t="s">
-        <v>551</v>
-      </c>
-      <c r="E158" s="6" t="s">
-        <v>552</v>
-      </c>
       <c r="F158" s="6" t="s">
-        <v>549</v>
+        <v>45</v>
       </c>
       <c r="G158" s="6" t="s">
         <v>15</v>
@@ -5971,19 +6089,19 @@
         <v>27</v>
       </c>
       <c r="B159" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="D159" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="C159" s="4" t="s">
+      <c r="E159" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="D159" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="E159" s="4" t="s">
-        <v>556</v>
-      </c>
       <c r="F159" s="4" t="s">
-        <v>557</v>
+        <v>236</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>15</v>
@@ -5999,16 +6117,16 @@
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="4" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>557</v>
+        <v>236</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>15</v>
@@ -6020,19 +6138,19 @@
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="E161" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="F161" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="D161" s="4" t="s">
-        <v>562</v>
-      </c>
-      <c r="E161" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="F161" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="G161" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H161" s="4"/>
       <c r="I161" s="4"/>
@@ -6041,16 +6159,16 @@
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="E162" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="D162" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="E162" s="4" t="s">
-        <v>566</v>
-      </c>
       <c r="F162" s="4" t="s">
-        <v>23</v>
+        <v>561</v>
       </c>
       <c r="G162" s="4" t="s">
         <v>24</v>
@@ -6062,16 +6180,16 @@
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="E163" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="D163" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="E163" s="4" t="s">
-        <v>569</v>
-      </c>
       <c r="F163" s="4" t="s">
-        <v>23</v>
+        <v>277</v>
       </c>
       <c r="G163" s="4" t="s">
         <v>24</v>
@@ -6083,19 +6201,19 @@
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="E164" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="D164" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="E164" s="4" t="s">
-        <v>572</v>
-      </c>
       <c r="F164" s="4" t="s">
-        <v>23</v>
+        <v>236</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H164" s="4"/>
       <c r="I164" s="4"/>
@@ -6105,22 +6223,22 @@
         <v>28</v>
       </c>
       <c r="B165" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D165" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="C165" s="6" t="s">
+      <c r="E165" s="6" t="s">
         <v>574</v>
       </c>
-      <c r="D165" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="E165" s="6" t="s">
-        <v>576</v>
-      </c>
       <c r="F165" s="6" t="s">
-        <v>228</v>
+        <v>38</v>
       </c>
       <c r="G165" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H165" s="6" t="s">
         <v>16</v>
@@ -6133,19 +6251,19 @@
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="E166" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="D166" s="6" t="s">
-        <v>578</v>
-      </c>
-      <c r="E166" s="6" t="s">
-        <v>579</v>
-      </c>
       <c r="F166" s="6" t="s">
-        <v>228</v>
+        <v>38</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H166" s="6"/>
       <c r="I166" s="6"/>
@@ -6154,19 +6272,19 @@
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="E167" s="6" t="s">
         <v>580</v>
       </c>
-      <c r="D167" s="6" t="s">
-        <v>581</v>
-      </c>
-      <c r="E167" s="6" t="s">
-        <v>582</v>
-      </c>
       <c r="F167" s="6" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="G167" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H167" s="6"/>
       <c r="I167" s="6"/>
@@ -6175,19 +6293,19 @@
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="E168" s="6" t="s">
         <v>583</v>
       </c>
-      <c r="D168" s="6" t="s">
-        <v>584</v>
-      </c>
-      <c r="E168" s="6" t="s">
-        <v>585</v>
-      </c>
       <c r="F168" s="6" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H168" s="6"/>
       <c r="I168" s="6"/>
@@ -6196,16 +6314,16 @@
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="E169" s="6" t="s">
         <v>586</v>
       </c>
-      <c r="D169" s="6" t="s">
+      <c r="F169" s="6" t="s">
         <v>587</v>
-      </c>
-      <c r="E169" s="6" t="s">
-        <v>588</v>
-      </c>
-      <c r="F169" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="G169" s="6" t="s">
         <v>15</v>
@@ -6217,16 +6335,16 @@
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="D170" s="6" t="s">
         <v>589</v>
       </c>
-      <c r="D170" s="6" t="s">
+      <c r="E170" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="E170" s="6" t="s">
-        <v>591</v>
-      </c>
       <c r="F170" s="6" t="s">
-        <v>205</v>
+        <v>587</v>
       </c>
       <c r="G170" s="6" t="s">
         <v>15</v>
@@ -6239,19 +6357,19 @@
         <v>29</v>
       </c>
       <c r="B171" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C171" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="C171" s="4" t="s">
+      <c r="D171" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="D171" s="4" t="s">
+      <c r="E171" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="E171" s="4" t="s">
+      <c r="F171" s="4" t="s">
         <v>595</v>
-      </c>
-      <c r="F171" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>15</v>
@@ -6276,7 +6394,7 @@
         <v>598</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>438</v>
+        <v>595</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>15</v>
@@ -6297,7 +6415,7 @@
         <v>601</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>24</v>
@@ -6318,10 +6436,10 @@
         <v>604</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>461</v>
+        <v>23</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H174" s="4"/>
       <c r="I174" s="4"/>
@@ -6339,7 +6457,7 @@
         <v>607</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>608</v>
+        <v>23</v>
       </c>
       <c r="G175" s="4" t="s">
         <v>24</v>
@@ -6351,16 +6469,16 @@
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="D176" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="D176" s="4" t="s">
+      <c r="E176" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="E176" s="4" t="s">
-        <v>611</v>
-      </c>
       <c r="F176" s="4" t="s">
-        <v>612</v>
+        <v>23</v>
       </c>
       <c r="G176" s="4" t="s">
         <v>24</v>
@@ -6373,22 +6491,22 @@
         <v>30</v>
       </c>
       <c r="B177" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="D177" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C177" s="6" t="s">
+      <c r="E177" s="6" t="s">
         <v>614</v>
       </c>
-      <c r="D177" s="6" t="s">
-        <v>615</v>
-      </c>
-      <c r="E177" s="6" t="s">
-        <v>616</v>
-      </c>
       <c r="F177" s="6" t="s">
-        <v>617</v>
+        <v>228</v>
       </c>
       <c r="G177" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H177" s="6" t="s">
         <v>16</v>
@@ -6401,19 +6519,19 @@
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="6" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>612</v>
+        <v>228</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H178" s="6"/>
       <c r="I178" s="6"/>
@@ -6422,19 +6540,19 @@
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="G179" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H179" s="6"/>
       <c r="I179" s="6"/>
@@ -6443,16 +6561,16 @@
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="6" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>612</v>
+        <v>99</v>
       </c>
       <c r="G180" s="6" t="s">
         <v>15</v>
@@ -6464,16 +6582,16 @@
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="6" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="G181" s="6" t="s">
         <v>15</v>
@@ -6485,25 +6603,293 @@
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="6" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>557</v>
+        <v>205</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H182" s="6"/>
       <c r="I182" s="6"/>
     </row>
+    <row r="183" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="3">
+        <v>31</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I183" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="G184" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H184" s="4"/>
+      <c r="I184" s="4"/>
+    </row>
+    <row r="185" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" s="3"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G185" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H185" s="4"/>
+      <c r="I185" s="4"/>
+    </row>
+    <row r="186" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" s="3"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="G186" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H186" s="4"/>
+      <c r="I186" s="4"/>
+    </row>
+    <row r="187" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" s="3"/>
+      <c r="B187" s="3"/>
+      <c r="C187" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="E187" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="G187" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H187" s="4"/>
+      <c r="I187" s="4"/>
+    </row>
+    <row r="188" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="3"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="G188" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H188" s="4"/>
+      <c r="I188" s="4"/>
+    </row>
+    <row r="189" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="5">
+        <v>32</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="F189" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="G189" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H189" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I189" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="5"/>
+      <c r="B190" s="5"/>
+      <c r="C190" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="G190" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H190" s="6"/>
+      <c r="I190" s="6"/>
+    </row>
+    <row r="191" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="5"/>
+      <c r="B191" s="5"/>
+      <c r="C191" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G191" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H191" s="6"/>
+      <c r="I191" s="6"/>
+    </row>
+    <row r="192" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="5"/>
+      <c r="B192" s="5"/>
+      <c r="C192" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="E192" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="G192" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H192" s="6"/>
+      <c r="I192" s="6"/>
+    </row>
+    <row r="193" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="5"/>
+      <c r="B193" s="5"/>
+      <c r="C193" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="F193" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G193" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H193" s="6"/>
+      <c r="I193" s="6"/>
+    </row>
+    <row r="194" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="5"/>
+      <c r="B194" s="5"/>
+      <c r="C194" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>670</v>
+      </c>
+      <c r="F194" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="G194" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H194" s="6"/>
+      <c r="I194" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="121">
+  <mergeCells count="129">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:A8"/>
     <mergeCell ref="B3:B8"/>
@@ -6625,6 +7011,14 @@
     <mergeCell ref="B177:B182"/>
     <mergeCell ref="H177:H182"/>
     <mergeCell ref="I177:I182"/>
+    <mergeCell ref="A183:A188"/>
+    <mergeCell ref="B183:B188"/>
+    <mergeCell ref="H183:H188"/>
+    <mergeCell ref="I183:I188"/>
+    <mergeCell ref="A189:A194"/>
+    <mergeCell ref="B189:B194"/>
+    <mergeCell ref="H189:H194"/>
+    <mergeCell ref="I189:I194"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
